--- a/bestsellers-clean.xlsx
+++ b/bestsellers-clean.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EQUIPO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E27754B-62F1-4CC9-BED7-8F46E1E50D68}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0471F4-BB74-485C-BE82-84AB651DEB58}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabla dinamica" sheetId="4" r:id="rId1"/>
-    <sheet name="Worksheet" sheetId="1" r:id="rId2"/>
+    <sheet name="Dataset" sheetId="1" r:id="rId2"/>
     <sheet name="Regresión" sheetId="3" r:id="rId3"/>
     <sheet name="Hoja1" sheetId="2" r:id="rId4"/>
+    <sheet name="Hoja4" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Worksheet!$A$2:$I$318</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Dataset!$A$2:$I$318</definedName>
   </definedNames>
   <calcPr calcId="179021"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId5"/>
+    <pivotCache cacheId="6" r:id="rId6"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -1916,7 +1917,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1931,7 +1932,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" pivotButton="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1990,6 +1990,392 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[bestsellers-clean.xlsx]Tabla dinamica!TablaDinámica3</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-CO"/>
+              <a:t>Promedio de calificación</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="es-CO" baseline="0"/>
+              <a:t> por rango de precio</a:t>
+            </a:r>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Tabla dinamica'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Tabla dinamica'!$A$4:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Alto</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Bajo</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Medio</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Tabla dinamica'!$B$4:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.6059405940594038</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.6142857142857139</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-24CD-4F69-A71F-8AD913A1E32B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="936437135"/>
+        <c:axId val="367030607"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="936437135"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="367030607"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="367030607"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="936437135"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-CO"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="es-ES"/>
@@ -4352,7 +4738,550 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4872,6 +5801,120 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>395287</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>395287</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8D79C53-60C6-4B8E-8C75-9AA1FE3268BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>771525</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="CuadroTexto 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A911292D-7B5C-4CEF-8C07-FA49471AE4C0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2000250" y="3257550"/>
+          <a:ext cx="8201025" cy="904875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-CO" sz="1400">
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>El gráfico muestra que el promedio de calificación de los libros se mantiene prácticamente constante entre los diferentes rangos de precio. Esto indica que no existe una relación directa entre el precio del libro y la percepción de calidad reflejada en el User Rating.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>476250</xdr:colOff>
       <xdr:row>2</xdr:row>
@@ -4909,10 +5952,59 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>163862</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>182090</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DD13910-55B8-4747-BB18-6497A5F18A0C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="13879862" cy="7992590"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="EQUIPO" refreshedDate="46063.418051157409" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="316" xr:uid="{3DF8D564-7FE1-4A58-9A9D-951F7B3C8D26}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A2:I318" sheet="Worksheet"/>
+    <worksheetSource ref="A2:I318" sheet="Dataset"/>
   </cacheSource>
   <cacheFields count="9">
     <cacheField name="Name" numFmtId="0">
@@ -8440,7 +9532,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F04B7A13-0352-44A6-9C66-595CF2A2D5C8}" name="TablaDinámica3" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Rango de precios">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F04B7A13-0352-44A6-9C66-595CF2A2D5C8}" name="TablaDinámica3" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" rowHeaderCaption="Rango de precios">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -8489,6 +9581,17 @@
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -8796,53 +9899,53 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>578</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>577</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>573</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="13">
         <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>574</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="14">
         <v>4.6059405940594038</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>575</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="14">
         <v>4.6142857142857139</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="12" t="s">
         <v>576</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="15">
         <v>4.6060897435897408</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I318"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8857,36 +9960,36 @@
         <v>541</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="2" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -8917,7 +10020,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -8948,7 +10051,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -8979,7 +10082,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -9010,7 +10113,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -9041,7 +10144,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -9072,7 +10175,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -9103,7 +10206,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -9134,7 +10237,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -9165,7 +10268,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -9196,7 +10299,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -9227,7 +10330,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -9258,7 +10361,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -9289,7 +10392,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -9320,7 +10423,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -9351,7 +10454,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -9382,7 +10485,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -9413,7 +10516,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -9444,7 +10547,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -9475,7 +10578,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>45</v>
       </c>
@@ -9506,7 +10609,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -9537,7 +10640,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -9568,7 +10671,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>51</v>
       </c>
@@ -9599,7 +10702,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>53</v>
       </c>
@@ -9630,7 +10733,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -9661,7 +10764,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>57</v>
       </c>
@@ -9692,7 +10795,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>59</v>
       </c>
@@ -9723,7 +10826,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -9754,7 +10857,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -9785,7 +10888,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -9816,7 +10919,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>66</v>
       </c>
@@ -9847,7 +10950,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>68</v>
       </c>
@@ -9878,7 +10981,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>70</v>
       </c>
@@ -9909,7 +11012,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>72</v>
       </c>
@@ -9940,7 +11043,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>74</v>
       </c>
@@ -9971,7 +11074,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -10002,7 +11105,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>77</v>
       </c>
@@ -10033,7 +11136,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -10064,7 +11167,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>81</v>
       </c>
@@ -10095,7 +11198,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>83</v>
       </c>
@@ -10126,7 +11229,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>85</v>
       </c>
@@ -10157,7 +11260,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>87</v>
       </c>
@@ -10188,7 +11291,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>89</v>
       </c>
@@ -10219,7 +11322,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>91</v>
       </c>
@@ -10250,7 +11353,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>93</v>
       </c>
@@ -10281,7 +11384,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -10312,7 +11415,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>97</v>
       </c>
@@ -10343,7 +11446,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -10374,7 +11477,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>100</v>
       </c>
@@ -10405,7 +11508,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>102</v>
       </c>
@@ -10436,7 +11539,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -10467,7 +11570,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>106</v>
       </c>
@@ -10498,7 +11601,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>107</v>
       </c>
@@ -10529,7 +11632,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -10560,7 +11663,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>110</v>
       </c>
@@ -10591,7 +11694,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>112</v>
       </c>
@@ -10622,7 +11725,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>114</v>
       </c>
@@ -10653,7 +11756,7 @@
         <v>Alto</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>116</v>
       </c>
@@ -10684,7 +11787,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>117</v>
       </c>
@@ -10715,7 +11818,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>118</v>
       </c>
@@ -10746,7 +11849,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>119</v>
       </c>
@@ -10777,7 +11880,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>121</v>
       </c>
@@ -10808,7 +11911,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>122</v>
       </c>
@@ -10839,7 +11942,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>123</v>
       </c>
@@ -10870,7 +11973,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>125</v>
       </c>
@@ -10901,7 +12004,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>126</v>
       </c>
@@ -10932,7 +12035,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>127</v>
       </c>
@@ -10963,7 +12066,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>129</v>
       </c>
@@ -10994,7 +12097,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>130</v>
       </c>
@@ -11025,7 +12128,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>131</v>
       </c>
@@ -11056,7 +12159,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>132</v>
       </c>
@@ -11087,7 +12190,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>133</v>
       </c>
@@ -11118,7 +12221,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>134</v>
       </c>
@@ -11149,7 +12252,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>135</v>
       </c>
@@ -11180,7 +12283,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>137</v>
       </c>
@@ -11211,7 +12314,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>139</v>
       </c>
@@ -11242,7 +12345,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>141</v>
       </c>
@@ -11273,7 +12376,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>142</v>
       </c>
@@ -11304,7 +12407,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>144</v>
       </c>
@@ -11335,7 +12438,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>145</v>
       </c>
@@ -11366,7 +12469,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>146</v>
       </c>
@@ -11397,7 +12500,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>148</v>
       </c>
@@ -11428,7 +12531,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>150</v>
       </c>
@@ -11459,7 +12562,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>152</v>
       </c>
@@ -11490,7 +12593,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>154</v>
       </c>
@@ -11521,7 +12624,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>156</v>
       </c>
@@ -11552,7 +12655,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>158</v>
       </c>
@@ -11583,7 +12686,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>159</v>
       </c>
@@ -11614,7 +12717,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>160</v>
       </c>
@@ -11645,7 +12748,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>161</v>
       </c>
@@ -11676,7 +12779,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>163</v>
       </c>
@@ -11707,7 +12810,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>165</v>
       </c>
@@ -11738,7 +12841,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>167</v>
       </c>
@@ -11769,7 +12872,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>169</v>
       </c>
@@ -11800,7 +12903,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>171</v>
       </c>
@@ -11831,7 +12934,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>173</v>
       </c>
@@ -11862,7 +12965,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>175</v>
       </c>
@@ -11893,7 +12996,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>177</v>
       </c>
@@ -11924,7 +13027,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>179</v>
       </c>
@@ -11955,7 +13058,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>181</v>
       </c>
@@ -11986,7 +13089,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>182</v>
       </c>
@@ -12017,7 +13120,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>183</v>
       </c>
@@ -12048,7 +13151,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>185</v>
       </c>
@@ -12079,7 +13182,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>187</v>
       </c>
@@ -12110,7 +13213,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>189</v>
       </c>
@@ -12141,7 +13244,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>191</v>
       </c>
@@ -12172,7 +13275,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>193</v>
       </c>
@@ -12203,7 +13306,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>195</v>
       </c>
@@ -12234,7 +13337,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>197</v>
       </c>
@@ -12265,7 +13368,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>199</v>
       </c>
@@ -12296,7 +13399,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>201</v>
       </c>
@@ -12327,7 +13430,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>202</v>
       </c>
@@ -12358,7 +13461,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>204</v>
       </c>
@@ -12389,7 +13492,7 @@
         <v>Medio</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>206</v>
       </c>
@@ -12420,7 +13523,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>208</v>
       </c>
@@ -12451,7 +13554,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>209</v>
       </c>
@@ -12482,7 +13585,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>210</v>
       </c>
@@ -12513,7 +13616,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>212</v>
       </c>
@@ -12544,7 +13647,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>213</v>
       </c>
@@ -12575,7 +13678,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>214</v>
       </c>
@@ -12606,7 +13709,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>216</v>
       </c>
@@ -12637,7 +13740,7 @@
         <v>Medio</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>217</v>
       </c>
@@ -12668,7 +13771,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>219</v>
       </c>
@@ -12699,7 +13802,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>221</v>
       </c>
@@ -12730,7 +13833,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>223</v>
       </c>
@@ -12761,7 +13864,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>225</v>
       </c>
@@ -12792,7 +13895,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>227</v>
       </c>
@@ -12823,7 +13926,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>229</v>
       </c>
@@ -12854,7 +13957,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>231</v>
       </c>
@@ -12885,7 +13988,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>232</v>
       </c>
@@ -12916,7 +14019,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>234</v>
       </c>
@@ -12947,7 +14050,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>236</v>
       </c>
@@ -12978,7 +14081,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>238</v>
       </c>
@@ -13009,7 +14112,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>240</v>
       </c>
@@ -13040,7 +14143,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>242</v>
       </c>
@@ -13071,7 +14174,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>244</v>
       </c>
@@ -13102,7 +14205,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>246</v>
       </c>
@@ -13133,7 +14236,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>248</v>
       </c>
@@ -13164,7 +14267,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>250</v>
       </c>
@@ -13195,7 +14298,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>252</v>
       </c>
@@ -13226,7 +14329,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>254</v>
       </c>
@@ -13257,7 +14360,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>255</v>
       </c>
@@ -13288,7 +14391,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>256</v>
       </c>
@@ -13319,7 +14422,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>258</v>
       </c>
@@ -13350,7 +14453,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>260</v>
       </c>
@@ -13381,7 +14484,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>261</v>
       </c>
@@ -13412,7 +14515,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>262</v>
       </c>
@@ -13443,7 +14546,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>263</v>
       </c>
@@ -13474,7 +14577,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>264</v>
       </c>
@@ -13505,7 +14608,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>265</v>
       </c>
@@ -13536,7 +14639,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>267</v>
       </c>
@@ -13567,7 +14670,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>269</v>
       </c>
@@ -13598,7 +14701,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>271</v>
       </c>
@@ -13629,7 +14732,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>272</v>
       </c>
@@ -13660,7 +14763,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>274</v>
       </c>
@@ -13691,7 +14794,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>276</v>
       </c>
@@ -13722,7 +14825,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>278</v>
       </c>
@@ -13753,7 +14856,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>280</v>
       </c>
@@ -13784,7 +14887,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>282</v>
       </c>
@@ -13815,7 +14918,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>284</v>
       </c>
@@ -13846,7 +14949,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>286</v>
       </c>
@@ -13877,7 +14980,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>288</v>
       </c>
@@ -13908,7 +15011,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>290</v>
       </c>
@@ -13939,7 +15042,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>292</v>
       </c>
@@ -13970,7 +15073,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>294</v>
       </c>
@@ -14001,7 +15104,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>295</v>
       </c>
@@ -14032,7 +15135,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>296</v>
       </c>
@@ -14063,7 +15166,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>298</v>
       </c>
@@ -14094,7 +15197,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>300</v>
       </c>
@@ -14125,7 +15228,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>302</v>
       </c>
@@ -14156,7 +15259,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>304</v>
       </c>
@@ -14187,7 +15290,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>306</v>
       </c>
@@ -14218,7 +15321,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>307</v>
       </c>
@@ -14249,7 +15352,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>309</v>
       </c>
@@ -14280,7 +15383,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>311</v>
       </c>
@@ -14311,7 +15414,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>312</v>
       </c>
@@ -14342,7 +15445,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>314</v>
       </c>
@@ -14373,7 +15476,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>316</v>
       </c>
@@ -14404,7 +15507,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>318</v>
       </c>
@@ -14435,7 +15538,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>320</v>
       </c>
@@ -14466,7 +15569,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>321</v>
       </c>
@@ -14497,7 +15600,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>323</v>
       </c>
@@ -14528,7 +15631,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>325</v>
       </c>
@@ -14559,7 +15662,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>326</v>
       </c>
@@ -14590,7 +15693,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>327</v>
       </c>
@@ -14621,7 +15724,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>329</v>
       </c>
@@ -14652,7 +15755,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>330</v>
       </c>
@@ -14683,7 +15786,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>332</v>
       </c>
@@ -14714,7 +15817,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>334</v>
       </c>
@@ -14745,7 +15848,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>336</v>
       </c>
@@ -14776,7 +15879,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>337</v>
       </c>
@@ -14807,7 +15910,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>339</v>
       </c>
@@ -14838,7 +15941,7 @@
         <v>Medio</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>341</v>
       </c>
@@ -14869,7 +15972,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>343</v>
       </c>
@@ -14900,7 +16003,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>345</v>
       </c>
@@ -14931,7 +16034,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>347</v>
       </c>
@@ -14962,7 +16065,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>349</v>
       </c>
@@ -14993,7 +16096,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>351</v>
       </c>
@@ -15024,7 +16127,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>352</v>
       </c>
@@ -15055,7 +16158,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>354</v>
       </c>
@@ -15086,7 +16189,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>356</v>
       </c>
@@ -15117,7 +16220,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>358</v>
       </c>
@@ -15148,7 +16251,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>359</v>
       </c>
@@ -15179,7 +16282,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>361</v>
       </c>
@@ -15210,7 +16313,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>363</v>
       </c>
@@ -15241,7 +16344,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>365</v>
       </c>
@@ -15272,7 +16375,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>366</v>
       </c>
@@ -15303,7 +16406,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>367</v>
       </c>
@@ -15334,7 +16437,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>368</v>
       </c>
@@ -15365,7 +16468,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>370</v>
       </c>
@@ -15396,7 +16499,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>372</v>
       </c>
@@ -15427,7 +16530,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>374</v>
       </c>
@@ -15458,7 +16561,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>376</v>
       </c>
@@ -15489,7 +16592,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>378</v>
       </c>
@@ -15520,7 +16623,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>380</v>
       </c>
@@ -15551,7 +16654,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>382</v>
       </c>
@@ -15582,7 +16685,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>384</v>
       </c>
@@ -15613,7 +16716,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>386</v>
       </c>
@@ -15644,7 +16747,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>388</v>
       </c>
@@ -15675,7 +16778,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>390</v>
       </c>
@@ -15706,7 +16809,7 @@
         <v>Medio</v>
       </c>
     </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>392</v>
       </c>
@@ -15737,7 +16840,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>394</v>
       </c>
@@ -15768,7 +16871,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>396</v>
       </c>
@@ -15799,7 +16902,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>398</v>
       </c>
@@ -15830,7 +16933,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>399</v>
       </c>
@@ -15861,7 +16964,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>401</v>
       </c>
@@ -15892,7 +16995,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>403</v>
       </c>
@@ -15923,7 +17026,7 @@
         <v>Medio</v>
       </c>
     </row>
-    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>405</v>
       </c>
@@ -15954,7 +17057,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>407</v>
       </c>
@@ -15985,7 +17088,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>409</v>
       </c>
@@ -16016,7 +17119,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>411</v>
       </c>
@@ -16047,7 +17150,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>412</v>
       </c>
@@ -16078,7 +17181,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>414</v>
       </c>
@@ -16109,7 +17212,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>416</v>
       </c>
@@ -16140,7 +17243,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>417</v>
       </c>
@@ -16172,7 +17275,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>419</v>
       </c>
@@ -16203,7 +17306,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>421</v>
       </c>
@@ -16234,7 +17337,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>423</v>
       </c>
@@ -16265,7 +17368,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>425</v>
       </c>
@@ -16296,7 +17399,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>427</v>
       </c>
@@ -16327,7 +17430,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>428</v>
       </c>
@@ -16358,7 +17461,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>430</v>
       </c>
@@ -16389,7 +17492,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>431</v>
       </c>
@@ -16420,7 +17523,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>433</v>
       </c>
@@ -16451,7 +17554,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>434</v>
       </c>
@@ -16482,7 +17585,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>436</v>
       </c>
@@ -16513,7 +17616,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>438</v>
       </c>
@@ -16544,7 +17647,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>439</v>
       </c>
@@ -16575,7 +17678,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>440</v>
       </c>
@@ -16606,7 +17709,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>441</v>
       </c>
@@ -16637,7 +17740,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>443</v>
       </c>
@@ -16668,7 +17771,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>445</v>
       </c>
@@ -16699,7 +17802,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>447</v>
       </c>
@@ -16730,7 +17833,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>448</v>
       </c>
@@ -16761,7 +17864,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>450</v>
       </c>
@@ -16792,7 +17895,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>452</v>
       </c>
@@ -16823,7 +17926,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>454</v>
       </c>
@@ -16854,7 +17957,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>456</v>
       </c>
@@ -16885,7 +17988,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>458</v>
       </c>
@@ -16916,7 +18019,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>459</v>
       </c>
@@ -16947,7 +18050,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>460</v>
       </c>
@@ -16978,7 +18081,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>461</v>
       </c>
@@ -17009,7 +18112,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>462</v>
       </c>
@@ -17040,7 +18143,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>464</v>
       </c>
@@ -17071,7 +18174,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>466</v>
       </c>
@@ -17102,7 +18205,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>468</v>
       </c>
@@ -17133,7 +18236,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>469</v>
       </c>
@@ -17164,7 +18267,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>471</v>
       </c>
@@ -17195,7 +18298,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>473</v>
       </c>
@@ -17226,7 +18329,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>475</v>
       </c>
@@ -17257,7 +18360,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>476</v>
       </c>
@@ -17288,7 +18391,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>477</v>
       </c>
@@ -17319,7 +18422,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>478</v>
       </c>
@@ -17350,7 +18453,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>480</v>
       </c>
@@ -17381,7 +18484,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>482</v>
       </c>
@@ -17412,7 +18515,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>483</v>
       </c>
@@ -17443,7 +18546,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>485</v>
       </c>
@@ -17474,7 +18577,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>487</v>
       </c>
@@ -17505,7 +18608,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>488</v>
       </c>
@@ -17536,7 +18639,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>490</v>
       </c>
@@ -17567,7 +18670,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>492</v>
       </c>
@@ -17598,7 +18701,7 @@
         <v>Medio</v>
       </c>
     </row>
-    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>494</v>
       </c>
@@ -17629,7 +18732,7 @@
         <v>Medio</v>
       </c>
     </row>
-    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>495</v>
       </c>
@@ -17660,7 +18763,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>497</v>
       </c>
@@ -17691,7 +18794,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>499</v>
       </c>
@@ -17722,7 +18825,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>500</v>
       </c>
@@ -17753,7 +18856,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>501</v>
       </c>
@@ -17784,7 +18887,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>503</v>
       </c>
@@ -17815,7 +18918,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>504</v>
       </c>
@@ -17846,7 +18949,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>506</v>
       </c>
@@ -17877,7 +18980,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>508</v>
       </c>
@@ -17908,7 +19011,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>509</v>
       </c>
@@ -17939,7 +19042,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>510</v>
       </c>
@@ -17970,7 +19073,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>511</v>
       </c>
@@ -18001,7 +19104,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>513</v>
       </c>
@@ -18032,7 +19135,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>514</v>
       </c>
@@ -18063,7 +19166,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>516</v>
       </c>
@@ -18094,7 +19197,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>517</v>
       </c>
@@ -18125,7 +19228,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>519</v>
       </c>
@@ -18156,7 +19259,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>520</v>
       </c>
@@ -18187,7 +19290,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>522</v>
       </c>
@@ -18218,7 +19321,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>523</v>
       </c>
@@ -18249,7 +19352,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>524</v>
       </c>
@@ -18280,7 +19383,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>525</v>
       </c>
@@ -18311,7 +19414,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>527</v>
       </c>
@@ -18342,7 +19445,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>528</v>
       </c>
@@ -18373,7 +19476,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>530</v>
       </c>
@@ -18404,7 +19507,7 @@
         <v>Alto</v>
       </c>
     </row>
-    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>531</v>
       </c>
@@ -18435,7 +19538,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>532</v>
       </c>
@@ -18466,7 +19569,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>534</v>
       </c>
@@ -18497,7 +19600,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>536</v>
       </c>
@@ -18528,7 +19631,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>538</v>
       </c>
@@ -18621,11 +19724,6 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter ref="A2:I318" xr:uid="{7DCF9891-846B-4372-97AA-2A5F577D685E}">
-    <filterColumn colId="8">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
   <mergeCells count="4">
     <mergeCell ref="A315:B315"/>
     <mergeCell ref="A316:B316"/>
@@ -21392,4 +22490,14 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3636FF-EA72-446F-96C9-43DA99D40845}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>